--- a/Input/urbs_intertemporal_2050/2025.xlsx
+++ b/Input/urbs_intertemporal_2050/2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\Input\urbs_intertemporal_2050\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9483B29-83DD-4F03-8CDF-E08005016DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11192D6B-3D59-43F4-8F65-E6BA315F25EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-1935" windowWidth="29040" windowHeight="17520" tabRatio="796" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="-5565" windowWidth="38640" windowHeight="21120" tabRatio="796" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="97">
   <si>
     <t>Property</t>
   </si>
@@ -181,9 +181,6 @@
     <t>Coal Plant</t>
   </si>
   <si>
-    <t>Coal Lignite</t>
-  </si>
-  <si>
     <t>Gas Plant (CCGT)</t>
   </si>
   <si>
@@ -319,36 +316,44 @@
     <t>EU27.Gas plant</t>
   </si>
   <si>
-    <t>Coal CCUS</t>
-  </si>
-  <si>
-    <t>Coal Lignite CCUS</t>
-  </si>
-  <si>
     <t>Gas Plant (CCGT) CCUS</t>
   </si>
   <si>
-    <t>Piped Gas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LNG </t>
-  </si>
-  <si>
-    <t>Gas Plant (CCGT) LNG</t>
+    <t>Lignite Plant</t>
+  </si>
+  <si>
+    <t>Other non-res</t>
+  </si>
+  <si>
+    <t>Oil Plant</t>
+  </si>
+  <si>
+    <t>Coal Plant CCUS</t>
+  </si>
+  <si>
+    <t>Lignite Plant CCUS</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Slack</t>
+  </si>
+  <si>
+    <t>Oil</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="#,##0.000"/>
     <numFmt numFmtId="168" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="31">
     <font>
@@ -554,7 +559,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="48">
+  <fills count="46">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -798,19 +803,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1348,7 +1341,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1479,13 +1472,11 @@
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="44" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1493,13 +1484,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" indent="2"/>
-    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="397">
     <cellStyle name="20% - Akzent1" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1900,7 +1885,296 @@
     <cellStyle name="Zelle überprüfen 4" xfId="214" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
     <cellStyle name="Zelle überprüfen 5" xfId="215" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="55">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <border>
         <top style="thin">
@@ -2447,7 +2721,7 @@
       <c r="A3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="61">
+      <c r="B3" s="59">
         <v>474000000</v>
       </c>
       <c r="C3" s="29" t="s">
@@ -2477,10 +2751,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="15" customFormat="1">
       <c r="A1" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2495,7 +2769,7 @@
       <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="60">
+      <c r="B3" s="58">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2503,7 +2777,7 @@
       <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="60">
+      <c r="B4" s="58">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2511,7 +2785,7 @@
       <c r="A5" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="60">
+      <c r="B5" s="58">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2519,7 +2793,7 @@
       <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B6" s="60">
+      <c r="B6" s="58">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2527,7 +2801,7 @@
       <c r="A7" s="5">
         <v>5</v>
       </c>
-      <c r="B7" s="60">
+      <c r="B7" s="58">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2535,7 +2809,7 @@
       <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="B8" s="60">
+      <c r="B8" s="58">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2543,7 +2817,7 @@
       <c r="A9" s="5">
         <v>7</v>
       </c>
-      <c r="B9" s="60">
+      <c r="B9" s="58">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2551,7 +2825,7 @@
       <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B10" s="60">
+      <c r="B10" s="58">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2559,7 +2833,7 @@
       <c r="A11" s="5">
         <v>9</v>
       </c>
-      <c r="B11" s="60">
+      <c r="B11" s="58">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2567,7 +2841,7 @@
       <c r="A12" s="5">
         <v>10</v>
       </c>
-      <c r="B12" s="60">
+      <c r="B12" s="58">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2575,7 +2849,7 @@
       <c r="A13" s="5">
         <v>11</v>
       </c>
-      <c r="B13" s="60">
+      <c r="B13" s="58">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2583,7 +2857,7 @@
       <c r="A14" s="5">
         <v>12</v>
       </c>
-      <c r="B14" s="60">
+      <c r="B14" s="58">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2607,13 +2881,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="15" customFormat="1">
       <c r="A1" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>85</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2632,13 +2906,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2690,7 +2964,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="3" customWidth="1"/>
@@ -2793,7 +3067,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>21</v>
@@ -2893,13 +3167,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D10">
-        <v>23.62</v>
+        <v>33.119999999999997</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>22</v>
@@ -2908,11 +3182,34 @@
         <v>22</v>
       </c>
     </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11">
+        <v>33.119999999999997</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B8:B10">
-    <cfRule type="expression" dxfId="22" priority="1">
+  <conditionalFormatting sqref="B8:B11">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B11">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations xWindow="307" yWindow="342" count="3">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Maximum commodity use per hour" prompt="For stock commodities, this value limits the energy use per hour (MW)._x000a_" sqref="F1" xr:uid="{737304EE-DF18-42D7-8893-3DE1D26EEDDE}"/>
@@ -2929,7 +3226,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="3" customWidth="1"/>
@@ -2994,29 +3291,29 @@
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="49" t="s">
-        <v>40</v>
+      <c r="B2" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="C2" s="20">
         <v>0</v>
       </c>
-      <c r="D2" s="55">
-        <v>46710</v>
+      <c r="D2" s="20">
+        <v>56122</v>
       </c>
       <c r="E2" s="50" t="s">
         <v>22</v>
       </c>
       <c r="F2" s="51">
-        <v>0</v>
-      </c>
-      <c r="G2" s="52">
-        <v>2731780.38</v>
-      </c>
-      <c r="H2" s="52">
-        <v>9923.6103600000006</v>
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="54">
+        <v>1784013.3447999998</v>
+      </c>
+      <c r="H2" s="55">
+        <v>28544.213516800002</v>
       </c>
       <c r="I2" s="52">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J2" s="53">
         <v>0</v>
@@ -3025,7 +3322,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="L2" s="53">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="M2" s="28" t="e">
         <v>#N/A</v>
@@ -3035,29 +3332,29 @@
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="49" t="s">
-        <v>41</v>
+      <c r="B3" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="C3" s="20">
         <v>0</v>
       </c>
-      <c r="D3" s="55">
-        <v>59840</v>
+      <c r="D3" s="20">
+        <v>43599</v>
       </c>
       <c r="E3" s="50" t="s">
         <v>22</v>
       </c>
       <c r="F3" s="51">
-        <v>0</v>
-      </c>
-      <c r="G3" s="53">
-        <v>3345037.2</v>
-      </c>
-      <c r="H3" s="53">
-        <v>28432.799999999999</v>
+        <v>0.65</v>
+      </c>
+      <c r="G3" s="52">
+        <v>2230016.6809999999</v>
+      </c>
+      <c r="H3" s="52">
+        <v>52182.390330800001</v>
       </c>
       <c r="I3" s="53">
-        <v>0.35699999999999998</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="J3" s="53">
         <v>0</v>
@@ -3066,7 +3363,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="L3" s="53">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M3" s="28" t="e">
         <v>#N/A</v>
@@ -3076,38 +3373,38 @@
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="49" t="s">
-        <v>42</v>
+      <c r="B4" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="C4" s="20">
         <v>0</v>
       </c>
-      <c r="D4" s="62">
+      <c r="D4" s="20">
         <v>999999</v>
       </c>
       <c r="E4" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="51">
-        <v>0.5</v>
-      </c>
-      <c r="G4" s="56">
-        <v>1784013.3448000001</v>
-      </c>
-      <c r="H4" s="57">
-        <v>28544.213516799999</v>
-      </c>
-      <c r="I4" s="52">
-        <v>2.7</v>
-      </c>
-      <c r="J4" s="53">
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="52">
+        <v>802808.92800000007</v>
+      </c>
+      <c r="H4" s="52">
+        <v>16725.186000000002</v>
+      </c>
+      <c r="I4" s="53">
+        <v>2.6</v>
+      </c>
+      <c r="J4" s="54">
         <v>0</v>
       </c>
       <c r="K4" s="42">
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="L4" s="53">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M4" s="28" t="e">
         <v>#N/A</v>
@@ -3117,38 +3414,38 @@
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="49" t="s">
-        <v>43</v>
+      <c r="B5" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="C5" s="20">
         <v>0</v>
       </c>
-      <c r="D5" s="62">
-        <v>999999</v>
+      <c r="D5" s="20">
+        <v>13483</v>
       </c>
       <c r="E5" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="51">
-        <v>0.65</v>
-      </c>
-      <c r="G5" s="52">
-        <v>2230016.6809999999</v>
-      </c>
-      <c r="H5" s="52">
-        <v>52182.390330800001</v>
-      </c>
-      <c r="I5" s="53">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="J5" s="53">
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>5648000</v>
+      </c>
+      <c r="H5" s="60">
+        <v>16725.186000000002</v>
+      </c>
+      <c r="I5">
+        <v>2.6</v>
+      </c>
+      <c r="J5" s="54">
         <v>0</v>
       </c>
       <c r="K5" s="42">
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="L5" s="53">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M5" s="28" t="e">
         <v>#N/A</v>
@@ -3158,31 +3455,31 @@
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="49" t="s">
-        <v>44</v>
+      <c r="B6" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="C6" s="20">
         <v>0</v>
       </c>
-      <c r="D6" s="62">
-        <v>999999</v>
+      <c r="D6" s="20">
+        <v>14578</v>
       </c>
       <c r="E6" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="51">
-        <v>0.25</v>
-      </c>
-      <c r="G6" s="52">
-        <v>802808.92800000007</v>
-      </c>
-      <c r="H6" s="52">
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>5648000</v>
+      </c>
+      <c r="H6" s="60">
         <v>16725.186000000002</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6">
         <v>2.6</v>
       </c>
-      <c r="J6" s="56">
+      <c r="J6" s="54">
         <v>0</v>
       </c>
       <c r="K6" s="42">
@@ -3199,38 +3496,38 @@
       <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="49" t="s">
-        <v>45</v>
+      <c r="B7" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="C7" s="20">
         <v>0</v>
       </c>
-      <c r="D7" s="54">
-        <v>94200</v>
+      <c r="D7" s="20">
+        <v>100000</v>
       </c>
       <c r="E7" s="50" t="s">
         <v>22</v>
       </c>
       <c r="F7" s="51">
-        <v>0</v>
-      </c>
-      <c r="G7" s="52">
-        <v>5909565.7200000007</v>
-      </c>
-      <c r="H7" s="57">
-        <v>133801.48800000001</v>
-      </c>
-      <c r="I7" s="52">
-        <v>7.1</v>
-      </c>
-      <c r="J7" s="53">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="53">
+        <v>3791028.3572399998</v>
+      </c>
+      <c r="H7" s="53">
+        <v>84183.129702000006</v>
+      </c>
+      <c r="I7" s="53">
+        <v>6.75</v>
+      </c>
+      <c r="J7" s="54">
         <v>0</v>
       </c>
       <c r="K7" s="42">
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="L7" s="53">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="M7" s="28" t="e">
         <v>#N/A</v>
@@ -3240,38 +3537,38 @@
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="49" t="s">
-        <v>46</v>
+      <c r="B8" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="C8" s="20">
         <v>0</v>
       </c>
       <c r="D8" s="20">
-        <v>999999999999</v>
+        <v>100000</v>
       </c>
       <c r="E8" s="50" t="s">
         <v>22</v>
       </c>
       <c r="F8" s="51">
-        <v>0</v>
-      </c>
-      <c r="G8" s="58">
-        <v>5648000</v>
-      </c>
-      <c r="H8" s="58">
-        <v>0</v>
-      </c>
-      <c r="I8" s="58">
-        <v>44.2</v>
-      </c>
-      <c r="J8" s="53">
+        <v>0.65</v>
+      </c>
+      <c r="G8" s="53">
+        <v>4014030.0248799999</v>
+      </c>
+      <c r="H8" s="53">
+        <v>76489.572146799997</v>
+      </c>
+      <c r="I8" s="53">
+        <v>6.96</v>
+      </c>
+      <c r="J8" s="54">
         <v>0</v>
       </c>
       <c r="K8" s="42">
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="L8" s="53">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="M8" s="28" t="e">
         <v>#N/A</v>
@@ -3281,38 +3578,38 @@
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="49" t="s">
-        <v>89</v>
+      <c r="B9" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="C9" s="20">
         <v>0</v>
       </c>
       <c r="D9" s="20">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="E9" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="51">
-        <v>0.5</v>
+      <c r="F9" s="3">
+        <v>0</v>
       </c>
       <c r="G9" s="53">
-        <v>3791028.3572399998</v>
+        <v>1951271.6999999997</v>
       </c>
       <c r="H9" s="53">
-        <v>84183.129702000006</v>
+        <v>45715.5</v>
       </c>
       <c r="I9" s="53">
-        <v>6.75</v>
-      </c>
-      <c r="J9" s="56">
+        <v>3.46</v>
+      </c>
+      <c r="J9" s="54">
         <v>0</v>
       </c>
       <c r="K9" s="42">
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="L9" s="53">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M9" s="28" t="e">
         <v>#N/A</v>
@@ -3323,37 +3620,37 @@
         <v>9</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="C10" s="20">
         <v>0</v>
       </c>
       <c r="D10" s="20">
-        <v>0</v>
+        <v>94198</v>
       </c>
       <c r="E10" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="51">
-        <v>0.65</v>
-      </c>
-      <c r="G10" s="53">
-        <v>4014030.0248799999</v>
-      </c>
-      <c r="H10" s="53">
-        <v>76489.572146799997</v>
-      </c>
-      <c r="I10" s="53">
-        <v>6.96</v>
-      </c>
-      <c r="J10" s="56">
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="52">
+        <v>5909565.7200000007</v>
+      </c>
+      <c r="H10" s="55">
+        <v>133801.48800000001</v>
+      </c>
+      <c r="I10" s="52">
+        <v>7.1</v>
+      </c>
+      <c r="J10" s="53">
         <v>0</v>
       </c>
       <c r="K10" s="42">
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="L10" s="53">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="M10" s="28" t="e">
         <v>#N/A</v>
@@ -3364,37 +3661,37 @@
         <v>9</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="C11" s="20">
         <v>0</v>
       </c>
       <c r="D11" s="20">
-        <v>0</v>
+        <v>46703</v>
       </c>
       <c r="E11" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="51">
-        <v>0.25</v>
-      </c>
-      <c r="G11" s="53">
-        <v>1951271.6999999997</v>
-      </c>
-      <c r="H11" s="53">
-        <v>45715.5</v>
-      </c>
-      <c r="I11" s="53">
-        <v>3.46</v>
-      </c>
-      <c r="J11" s="56">
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="52">
+        <v>2731780.3800000004</v>
+      </c>
+      <c r="H11" s="52">
+        <v>9923.6103600000006</v>
+      </c>
+      <c r="I11" s="52">
+        <v>0</v>
+      </c>
+      <c r="J11" s="53">
         <v>0</v>
       </c>
       <c r="K11" s="42">
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="L11" s="53">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="M11" s="28" t="e">
         <v>#N/A</v>
@@ -3404,72 +3701,168 @@
       <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="59" t="s">
-        <v>94</v>
+      <c r="B12" s="49" t="s">
+        <v>41</v>
       </c>
       <c r="C12" s="20">
         <v>0</v>
       </c>
-      <c r="D12" s="62">
-        <v>999999</v>
+      <c r="D12" s="20">
+        <v>61218</v>
       </c>
       <c r="E12" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="51">
-        <v>0.25</v>
-      </c>
-      <c r="G12" s="52">
-        <v>802808.92800000007</v>
-      </c>
-      <c r="H12" s="52">
-        <v>16725.186000000002</v>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="53">
+        <v>3345037.2</v>
+      </c>
+      <c r="H12" s="53">
+        <v>28432.799999999999</v>
       </c>
       <c r="I12" s="53">
-        <v>2.6</v>
-      </c>
-      <c r="J12" s="56">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="J12" s="53">
         <v>0</v>
       </c>
       <c r="K12" s="42">
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="L12" s="53">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M12" s="28" t="e">
         <v>#N/A</v>
       </c>
     </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="20">
+        <v>0</v>
+      </c>
+      <c r="D13" s="20">
+        <v>999999</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="56">
+        <v>5648000</v>
+      </c>
+      <c r="H13" s="56">
+        <v>0</v>
+      </c>
+      <c r="I13" s="56">
+        <v>44.2</v>
+      </c>
+      <c r="J13" s="53">
+        <v>0</v>
+      </c>
+      <c r="K13" s="42">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="L13" s="53">
+        <v>25</v>
+      </c>
+      <c r="M13" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
-  <conditionalFormatting sqref="A2:B4 P2:XFD4 A2:A12 C2:C12">
-    <cfRule type="expression" dxfId="21" priority="9">
+  <conditionalFormatting sqref="P2:XFD4">
+    <cfRule type="expression" dxfId="53" priority="24">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:XFD1 N12:XFD12 A13:XFD1048576">
-    <cfRule type="expression" dxfId="20" priority="21">
+  <conditionalFormatting sqref="A1:XFD1 A14:XFD1048576 N12:XFD13">
+    <cfRule type="expression" dxfId="52" priority="36">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B12">
+  <conditionalFormatting sqref="C2:D13 F9:F13 F4:F6">
+    <cfRule type="expression" dxfId="33" priority="15">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E4 E12:E13">
+    <cfRule type="expression" dxfId="32" priority="14">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2">
+    <cfRule type="expression" dxfId="31" priority="13">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
+    <cfRule type="expression" dxfId="30" priority="12">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11:M11">
+    <cfRule type="expression" dxfId="29" priority="11">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11:I11">
+    <cfRule type="expression" dxfId="28" priority="10">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:M12">
+    <cfRule type="expression" dxfId="27" priority="9">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:M2">
+    <cfRule type="expression" dxfId="26" priority="8">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B9">
+    <cfRule type="expression" dxfId="25" priority="7">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A4">
+    <cfRule type="expression" dxfId="24" priority="6">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A13">
+    <cfRule type="expression" dxfId="23" priority="5">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="expression" dxfId="22" priority="4">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B12">
+    <cfRule type="expression" dxfId="21" priority="3">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B12">
+    <cfRule type="expression" dxfId="20" priority="2">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
     <cfRule type="expression" dxfId="19" priority="1">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:M3 E4:M4">
-    <cfRule type="expression" dxfId="18" priority="17">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D8:D11">
-    <cfRule type="expression" dxfId="17" priority="3">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:I2">
-    <cfRule type="expression" dxfId="16" priority="14">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3496,7 +3889,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -3516,24 +3909,24 @@
         <v>11</v>
       </c>
       <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="18" t="s">
-        <v>49</v>
-      </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="59" t="s">
-        <v>43</v>
+      <c r="A2" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" s="24">
         <v>1</v>
@@ -3543,14 +3936,14 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="59" t="s">
-        <v>43</v>
+      <c r="A3" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" s="24">
         <v>0.41</v>
@@ -3561,14 +3954,14 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="59" t="s">
-        <v>43</v>
+      <c r="A4" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" s="24">
         <v>0.36299999999999999</v>
@@ -3578,32 +3971,32 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="59" t="s">
-        <v>44</v>
+      <c r="A5" s="57" t="s">
+        <v>43</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D5" s="24">
         <v>1</v>
       </c>
       <c r="E5" s="24" t="e">
-        <f>NA()</f>
+        <f>D5*E3</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="59" t="s">
-        <v>44</v>
+      <c r="A6" s="57" t="s">
+        <v>43</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D6" s="24">
         <v>0.6</v>
@@ -3614,32 +4007,32 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="59" t="s">
-        <v>44</v>
+      <c r="A7" s="57" t="s">
+        <v>43</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D7" s="24">
         <v>0.20499999999999999</v>
       </c>
       <c r="E7" s="24" t="e">
-        <f>NA()</f>
+        <f>D7*E5</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="59" t="s">
-        <v>46</v>
+      <c r="A8" s="57" t="s">
+        <v>45</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="24">
         <v>1</v>
@@ -3650,14 +4043,14 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="59" t="s">
-        <v>46</v>
+      <c r="A9" s="57" t="s">
+        <v>45</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="24">
         <v>0.35</v>
@@ -3668,14 +4061,14 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="59" t="s">
-        <v>46</v>
+      <c r="A10" s="57" t="s">
+        <v>45</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="24">
         <v>0</v>
@@ -3686,14 +4079,14 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="59" t="s">
-        <v>45</v>
+      <c r="A11" s="57" t="s">
+        <v>44</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" s="24">
         <v>1</v>
@@ -3704,14 +4097,14 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="59" t="s">
-        <v>45</v>
+      <c r="A12" s="57" t="s">
+        <v>44</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" s="24">
         <v>0.38</v>
@@ -3722,14 +4115,14 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="57" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="24">
         <v>1</v>
@@ -3739,14 +4132,14 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="59" t="s">
+      <c r="A14" s="57" t="s">
         <v>42</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" s="24">
         <v>0.45</v>
@@ -3757,14 +4150,14 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="57" t="s">
         <v>42</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" s="24">
         <v>0.34179999999999999</v>
@@ -3775,14 +4168,14 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="57" t="s">
         <v>40</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" s="24">
         <v>1</v>
@@ -3793,14 +4186,14 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="59" t="s">
+      <c r="A17" s="57" t="s">
         <v>40</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D17" s="24">
         <v>1</v>
@@ -3811,14 +4204,14 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="59" t="s">
+      <c r="A18" s="57" t="s">
         <v>41</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" s="24">
         <v>1</v>
@@ -3829,14 +4222,14 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="57" t="s">
         <v>41</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="24">
         <v>1</v>
@@ -3847,14 +4240,14 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="59" t="s">
-        <v>89</v>
+      <c r="A20" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" s="24">
         <v>1</v>
@@ -3865,16 +4258,16 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="59" t="s">
-        <v>89</v>
+      <c r="A21" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="63">
+        <v>50</v>
+      </c>
+      <c r="D21" s="24">
         <v>0.36</v>
       </c>
       <c r="E21" s="24" t="e">
@@ -3883,16 +4276,16 @@
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="59" t="s">
-        <v>89</v>
+      <c r="A22" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="64">
+        <v>50</v>
+      </c>
+      <c r="D22" s="24">
         <v>3.4180000000000002E-2</v>
       </c>
       <c r="E22" s="24" t="e">
@@ -3901,14 +4294,14 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="59" t="s">
-        <v>90</v>
+      <c r="A23" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D23" s="24">
         <v>1</v>
@@ -3919,16 +4312,16 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="59" t="s">
-        <v>90</v>
+      <c r="A24" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="63">
+        <v>50</v>
+      </c>
+      <c r="D24" s="24">
         <v>0.32</v>
       </c>
       <c r="E24" s="24" t="e">
@@ -3937,16 +4330,16 @@
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="59" t="s">
-        <v>90</v>
+      <c r="A25" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="64">
+        <v>50</v>
+      </c>
+      <c r="D25" s="24">
         <v>3.6299999999999999E-2</v>
       </c>
       <c r="E25" s="24" t="e">
@@ -3955,34 +4348,34 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="59" t="s">
-        <v>91</v>
+      <c r="A26" s="57" t="s">
+        <v>88</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D26" s="24">
         <v>1</v>
       </c>
       <c r="E26" s="24" t="e">
-        <f>NA()</f>
+        <f>D26*E24</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="59" t="s">
-        <v>91</v>
+      <c r="A27" s="57" t="s">
+        <v>88</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="63">
+        <v>50</v>
+      </c>
+      <c r="D27" s="24">
         <v>0.4</v>
       </c>
       <c r="E27" s="24" t="e">
@@ -3991,16 +4384,16 @@
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="59" t="s">
-        <v>91</v>
+      <c r="A28" s="57" t="s">
+        <v>88</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="64">
+        <v>50</v>
+      </c>
+      <c r="D28" s="24">
         <v>2.0500000000000001E-2</v>
       </c>
       <c r="E28" s="24" t="e">
@@ -4009,34 +4402,35 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="59" t="s">
-        <v>94</v>
+      <c r="A29" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" s="24">
         <v>1</v>
       </c>
-      <c r="E29" s="24">
-        <v>1.2</v>
+      <c r="E29" s="24" t="e">
+        <f>D29*E27</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="59" t="s">
-        <v>94</v>
+      <c r="A30" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D30" s="24">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E30" s="24" t="e">
         <f>NA()</f>
@@ -4044,56 +4438,90 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="59" t="s">
-        <v>94</v>
+      <c r="A31" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D31" s="24">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="E31" s="24">
-        <f>D31*E29</f>
-        <v>0.24599999999999997</v>
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="E31" s="24" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="24">
+        <v>1</v>
+      </c>
+      <c r="E32" s="24" t="e">
+        <f>D32*E30</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="E33" s="24" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="24">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="E34" s="24" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5 C5:D5 A8:XFD19 F20:XFD31 A32:XFD1048576 A6:D7 F5:XFD7">
-    <cfRule type="expression" dxfId="15" priority="33">
+  <conditionalFormatting sqref="A35:XFD1048576 F8:XFD34">
+    <cfRule type="expression" dxfId="47" priority="74">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:XFD4 A20:A29 A30:C31 E30:E31">
-    <cfRule type="expression" dxfId="14" priority="10">
+  <conditionalFormatting sqref="A1:XFD1 F2:XFD4">
+    <cfRule type="expression" dxfId="46" priority="51">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B21:C25 C26:D26 B27:C27">
-    <cfRule type="expression" dxfId="13" priority="25">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B28:D28">
-    <cfRule type="expression" dxfId="12" priority="12">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B20:E20 D23:E23">
-    <cfRule type="expression" dxfId="11" priority="26">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B29:E29">
-    <cfRule type="expression" dxfId="10" priority="5">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D19 E2:E4">
-    <cfRule type="dataBar" priority="42">
+  <conditionalFormatting sqref="D1:E1">
+    <cfRule type="dataBar" priority="108">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -4101,61 +4529,247 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4">
+  <conditionalFormatting sqref="D35:E1048576">
+    <cfRule type="dataBar" priority="115">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:XFD7">
+    <cfRule type="expression" dxfId="36" priority="44">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D19 A5 A6:C19 E6:E19 B2:C4 E2:E4">
+    <cfRule type="expression" dxfId="18" priority="35">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21:C25 C26 B27:C27">
+    <cfRule type="expression" dxfId="17" priority="26">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20:C20 A26:A28 E23 E20">
+    <cfRule type="expression" dxfId="16" priority="27">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5:E5">
+    <cfRule type="expression" dxfId="15" priority="20">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6:D7">
+    <cfRule type="dataBar" priority="33">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{23B6D87E-01FF-4CAA-AC24-3EC68B3B5B2E}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:D10 D5 E3:E4 E6:E7">
+    <cfRule type="dataBar" priority="40">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{B33FB1A8-C86E-45EF-9736-7042E56B7C86}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13 D15">
+    <cfRule type="dataBar" priority="32">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{FF0F0CEF-0088-4FF8-A7CC-5D5815BB9571}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15">
+    <cfRule type="dataBar" priority="31">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{BDC0B1CD-291E-42B5-A8F3-C064C2FB35DE}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:E2 D3:D19">
+    <cfRule type="dataBar" priority="34">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DF5A14F6-FAEA-436D-BC3B-FE807CD1C0A0}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11:E12">
+    <cfRule type="dataBar" priority="41">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D9EBA9A9-9505-4048-9C9E-8395F46E93A9}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16:E17">
+    <cfRule type="dataBar" priority="37">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{BDE9B354-9B0D-4204-8BBE-8620109545F8}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18:E19">
+    <cfRule type="dataBar" priority="36">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{FEDE11E8-4678-4877-92F5-E4671315133C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5">
+    <cfRule type="dataBar" priority="21">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F4097541-4EFE-4D6C-86A7-318D200AE9A2}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:E10">
+    <cfRule type="dataBar" priority="39">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{EF47B776-A1AC-4613-A427-0670040A3FCB}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13:E15">
     <cfRule type="dataBar" priority="38">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
         <color rgb="FF638EC6"/>
       </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D6:D7">
-    <cfRule type="dataBar" priority="36">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{ED5F02D3-ADDF-45CF-ABD6-541056C7B9C6}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20:E22">
+    <cfRule type="dataBar" priority="30">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
         <color rgb="FF638EC6"/>
       </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D15 D13">
-    <cfRule type="dataBar" priority="34">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{3A01995E-DE0A-466C-B2F1-14320DE2D1EB}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21:E22">
+    <cfRule type="expression" dxfId="14" priority="25">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E23:E24">
+    <cfRule type="dataBar" priority="29">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
         <color rgb="FF638EC6"/>
       </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D15">
-    <cfRule type="dataBar" priority="32">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F1D82E9E-696A-4AF9-B2D0-23EA3BB9E23F}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E24:E34">
+    <cfRule type="expression" dxfId="13" priority="19">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E25:E26">
+    <cfRule type="dataBar" priority="24">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
         <color rgb="FF638EC6"/>
       </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D16:D17">
-    <cfRule type="dataBar" priority="41">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D18:D19">
-    <cfRule type="dataBar" priority="40">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D20">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2F7AA45E-FAEA-4DE1-A31E-52C65BF9B9F8}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E27">
     <cfRule type="dataBar" priority="28">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -4164,13 +4778,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{FE60BBE6-13B4-4FBC-85D1-9C9C42983FFA}</x14:id>
+          <x14:id>{5BEB5901-1F15-429A-8BB1-438A55C69C80}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D22">
-    <cfRule type="dataBar" priority="17">
+  <conditionalFormatting sqref="E28">
+    <cfRule type="dataBar" priority="23">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -4178,82 +4792,37 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{DC555EA0-E0A3-4937-8DAA-09AB73E812C1}</x14:id>
+          <x14:id>{1A8E9B7E-1C74-4466-A95D-5E43B4E98982}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="18">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28:C28">
+    <cfRule type="expression" dxfId="12" priority="22">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
-    <cfRule type="dataBar" priority="19">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C373837E-C69E-4E58-B11F-98F40706E997}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D23">
-    <cfRule type="dataBar" priority="27">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{17A80BF5-4F14-49E0-A552-F5EF53DAAFE1}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D25">
-    <cfRule type="dataBar" priority="14">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{AD5BF277-31E2-42C0-A967-E768405FD40A}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="15">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A4">
+    <cfRule type="expression" dxfId="11" priority="18">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
-    <cfRule type="dataBar" priority="16">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A377CCC3-5A9C-46C9-8803-5FD6731C3849}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D28">
-    <cfRule type="dataBar" priority="11">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D3D934C3-A578-4A49-B389-22CB0C475535}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29:A31">
+    <cfRule type="expression" dxfId="10" priority="17">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A32:A34">
+    <cfRule type="expression" dxfId="9" priority="16">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29 B30:C30">
+    <cfRule type="expression" dxfId="8" priority="14">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29">
     <cfRule type="dataBar" priority="13">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -4262,16 +4831,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{52C1D05A-E946-4407-8E8D-7704136AF907}</x14:id>
+          <x14:id>{38A3C364-17B6-4C9E-952F-95F9EDFF4919}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D29:D31">
-    <cfRule type="expression" dxfId="7" priority="6">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-    <cfRule type="dataBar" priority="9">
+  <conditionalFormatting sqref="E30">
+    <cfRule type="dataBar" priority="15">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -4279,12 +4845,64 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E8059422-031D-423F-B0DB-9B02EF46DC1A}</x14:id>
+          <x14:id>{D1FB9B9D-E59E-4793-A486-3A6B64AC1628}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D30:D31">
+  <conditionalFormatting sqref="E31">
+    <cfRule type="dataBar" priority="12">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{482D1302-BF25-4BED-A0AF-EE8C510D6066}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:C31">
+    <cfRule type="expression" dxfId="7" priority="11">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C32 B33:C33">
+    <cfRule type="expression" dxfId="6" priority="9">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E32">
+    <cfRule type="dataBar" priority="8">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F08AA4F7-1C47-44B6-BB32-6CC35B2DC34A}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E33">
+    <cfRule type="dataBar" priority="10">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DBB2403E-50F8-4FDE-8806-94CB090EDB5C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E34">
     <cfRule type="dataBar" priority="7">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -4293,22 +4911,33 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A5AFB825-13C6-426B-B7F5-6402B0B447A7}</x14:id>
+          <x14:id>{1F5E308D-2ADF-47B4-9B05-E17826909C6F}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:E1">
-    <cfRule type="dataBar" priority="67">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D26">
-    <cfRule type="dataBar" priority="29">
+  <conditionalFormatting sqref="B34:C34">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:A22">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20:D34">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20:D34">
+    <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -4316,13 +4945,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{BA489CCE-F559-44AD-8A75-1E9B55195C33}</x14:id>
+          <x14:id>{AD1BF178-371A-4438-B47F-1E6A4B5A3A75}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D29:E29 E30:E31">
-    <cfRule type="dataBar" priority="8">
+  <conditionalFormatting sqref="D20:D34">
+    <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -4330,151 +4959,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{BC50BDC4-63AC-41EE-94E5-E5396C6A4BC3}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D32:E1048576">
-    <cfRule type="dataBar" priority="74">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E10">
-    <cfRule type="dataBar" priority="50">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11:E12">
-    <cfRule type="dataBar" priority="53">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13:E15">
-    <cfRule type="dataBar" priority="48">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16:E17">
-    <cfRule type="dataBar" priority="47">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E18:E19">
-    <cfRule type="dataBar" priority="46">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E20:E22">
-    <cfRule type="dataBar" priority="31">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8C9791CD-D2D9-4A28-8FD9-974C227D0DAE}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E21:E22">
-    <cfRule type="expression" dxfId="6" priority="24">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E23:E24">
-    <cfRule type="dataBar" priority="30">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7A12A122-A5C3-4A6B-A77D-1A7781DED8CD}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E24:E25">
-    <cfRule type="expression" dxfId="5" priority="22">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E25">
-    <cfRule type="dataBar" priority="23">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{DDB2FA35-E285-4768-93C8-24BA0BFCF641}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E7">
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E7">
-    <cfRule type="dataBar" priority="4">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{97D885F7-376B-4DFA-ADB1-4A8DF44D7FED}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E26:E28">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E26:E28">
-    <cfRule type="dataBar" priority="2">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{22E43252-B12B-4364-B80D-1F8847C3058E}</x14:id>
+          <x14:id>{97C8A1B8-CF7E-4BFD-B0AB-30267FAA4149}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4489,7 +4974,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{FE60BBE6-13B4-4FBC-85D1-9C9C42983FFA}">
+          <x14:cfRule type="dataBar" id="{23B6D87E-01FF-4CAA-AC24-3EC68B3B5B2E}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4501,10 +4986,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D20</xm:sqref>
+          <xm:sqref>D6:D7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{DC555EA0-E0A3-4937-8DAA-09AB73E812C1}">
+          <x14:cfRule type="dataBar" id="{B33FB1A8-C86E-45EF-9736-7042E56B7C86}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4516,7 +5001,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{C373837E-C69E-4E58-B11F-98F40706E997}">
+          <xm:sqref>D8:D10 D5 E3:E4 E6:E7</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{FF0F0CEF-0088-4FF8-A7CC-5D5815BB9571}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4528,10 +5016,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D22</xm:sqref>
+          <xm:sqref>D13 D15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{17A80BF5-4F14-49E0-A552-F5EF53DAAFE1}">
+          <x14:cfRule type="dataBar" id="{BDC0B1CD-291E-42B5-A8F3-C064C2FB35DE}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4543,10 +5031,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D23</xm:sqref>
+          <xm:sqref>D15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{AD5BF277-31E2-42C0-A967-E768405FD40A}">
+          <x14:cfRule type="dataBar" id="{DF5A14F6-FAEA-436D-BC3B-FE807CD1C0A0}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4558,7 +5046,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{A377CCC3-5A9C-46C9-8803-5FD6731C3849}">
+          <xm:sqref>D2:E2 D3:D19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D9EBA9A9-9505-4048-9C9E-8395F46E93A9}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4570,10 +5061,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D25</xm:sqref>
+          <xm:sqref>D11:E12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D3D934C3-A578-4A49-B389-22CB0C475535}">
+          <x14:cfRule type="dataBar" id="{BDE9B354-9B0D-4204-8BBE-8620109545F8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4585,7 +5076,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{52C1D05A-E946-4407-8E8D-7704136AF907}">
+          <xm:sqref>D16:E17</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{FEDE11E8-4678-4877-92F5-E4671315133C}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4597,10 +5091,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D28</xm:sqref>
+          <xm:sqref>D18:E19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{E8059422-031D-423F-B0DB-9B02EF46DC1A}">
+          <x14:cfRule type="dataBar" id="{F4097541-4EFE-4D6C-86A7-318D200AE9A2}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4612,10 +5106,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D29:D31</xm:sqref>
+          <xm:sqref>E5</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{A5AFB825-13C6-426B-B7F5-6402B0B447A7}">
+          <x14:cfRule type="dataBar" id="{EF47B776-A1AC-4613-A427-0670040A3FCB}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4627,10 +5121,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D30:D31</xm:sqref>
+          <xm:sqref>E8:E10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{BA489CCE-F559-44AD-8A75-1E9B55195C33}">
+          <x14:cfRule type="dataBar" id="{ED5F02D3-ADDF-45CF-ABD6-541056C7B9C6}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4642,25 +5136,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D26</xm:sqref>
+          <xm:sqref>E13:E15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{BC50BDC4-63AC-41EE-94E5-E5396C6A4BC3}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>2</xm:f>
-              </x14:cfvo>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>D29:E29 E30:E31</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8C9791CD-D2D9-4A28-8FD9-974C227D0DAE}">
+          <x14:cfRule type="dataBar" id="{3A01995E-DE0A-466C-B2F1-14320DE2D1EB}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4675,7 +5154,7 @@
           <xm:sqref>E20:E22</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7A12A122-A5C3-4A6B-A77D-1A7781DED8CD}">
+          <x14:cfRule type="dataBar" id="{F1D82E9E-696A-4AF9-B2D0-23EA3BB9E23F}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4690,7 +5169,7 @@
           <xm:sqref>E23:E24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{DDB2FA35-E285-4768-93C8-24BA0BFCF641}">
+          <x14:cfRule type="dataBar" id="{2F7AA45E-FAEA-4DE1-A31E-52C65BF9B9F8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4702,10 +5181,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E25</xm:sqref>
+          <xm:sqref>E25:E26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{97D885F7-376B-4DFA-ADB1-4A8DF44D7FED}">
+          <x14:cfRule type="dataBar" id="{5BEB5901-1F15-429A-8BB1-438A55C69C80}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4717,10 +5196,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E5:E7</xm:sqref>
+          <xm:sqref>E27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{22E43252-B12B-4364-B80D-1F8847C3058E}">
+          <x14:cfRule type="dataBar" id="{1A8E9B7E-1C74-4466-A95D-5E43B4E98982}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4732,7 +5211,127 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E26:E28</xm:sqref>
+          <xm:sqref>E28</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{38A3C364-17B6-4C9E-952F-95F9EDFF4919}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E29</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D1FB9B9D-E59E-4793-A486-3A6B64AC1628}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E30</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{482D1302-BF25-4BED-A0AF-EE8C510D6066}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E31</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{F08AA4F7-1C47-44B6-BB32-6CC35B2DC34A}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E32</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{DBB2403E-50F8-4FDE-8806-94CB090EDB5C}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E33</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{1F5E308D-2ADF-47B4-9B05-E17826909C6F}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{AD1BF178-371A-4438-B47F-1E6A4B5A3A75}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D20:D34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{97C8A1B8-CF7E-4BFD-B0AB-30267FAA4149}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D20:D34</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -4764,19 +5363,19 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>53</v>
-      </c>
-      <c r="C1" t="s">
-        <v>54</v>
       </c>
       <c r="D1" t="s">
         <v>11</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F1" s="17" t="s">
         <v>33</v>
@@ -4800,19 +5399,19 @@
         <v>38</v>
       </c>
       <c r="M1" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N1" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>57</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <conditionalFormatting sqref="K1">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4868,46 +5467,46 @@
         <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D1" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="G1" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="H1" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="J1" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="K1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="L1" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="M1" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="N1" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>70</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>71</v>
       </c>
       <c r="P1" s="16" t="s">
         <v>37</v>
@@ -4916,13 +5515,13 @@
         <v>38</v>
       </c>
       <c r="R1" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="S1" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="S1" s="16" t="s">
+      <c r="T1" s="36" t="s">
         <v>73</v>
-      </c>
-      <c r="T1" s="36" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -4930,7 +5529,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" s="41" t="s">
         <v>18</v>
@@ -4990,7 +5589,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" s="41" t="s">
         <v>18</v>
@@ -5051,7 +5650,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" s="41" t="s">
         <v>18</v>
@@ -5112,7 +5711,7 @@
   </sheetData>
   <autoFilter ref="A1:R1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <conditionalFormatting sqref="P1">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="34" priority="3">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5164,19 +5763,19 @@
         <v>11</v>
       </c>
       <c r="C1" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="G1" s="17" t="s">
         <v>80</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -5218,10 +5817,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2">
